--- a/docs/import-examples/01 Menu items.xlsx
+++ b/docs/import-examples/01 Menu items.xlsx
@@ -621,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L505"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -673,11 +673,196 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="5:8" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3">
+        <v>45</v>
+      </c>
+      <c r="J3">
+        <v>120</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>55</v>
+      </c>
+      <c r="J5">
+        <v>140</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>40</v>
+      </c>
+      <c r="J6">
+        <v>110</v>
+      </c>
+      <c r="K6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="7" spans="5:8" x14ac:dyDescent="0.25"/>
     <row r="8" spans="5:8" x14ac:dyDescent="0.25"/>
     <row r="9" spans="5:8" x14ac:dyDescent="0.25"/>
@@ -972,414 +1157,24 @@
     <row r="298" spans="5:8" x14ac:dyDescent="0.25"/>
     <row r="299" spans="5:8" x14ac:dyDescent="0.25"/>
     <row r="300" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="305" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="308" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="309" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="310" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="311" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="312" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="313" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="314" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="315" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="316" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="317" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="320" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="332" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="333" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="334" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="335" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="336" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="337" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="339" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="340" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="342" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="343" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="344" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="345" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="346" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="347" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="348" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="349" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="350" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="352" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="353" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="354" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="355" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="356" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="357" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="358" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="359" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="360" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="361" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="362" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="364" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="366" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="367" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="368" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="369" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="370" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="371" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="372" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="373" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="374" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="375" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="376" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="377" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="378" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="379" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="380" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="381" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="382" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="383" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="384" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="386" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="387" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="388" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="390" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="391" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="393" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="394" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="395" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="396" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="397" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="398" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="399" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="400" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="401" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="402" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="403" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="404" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="405" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="406" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="407" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="408" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="409" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="410" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="411" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="412" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="413" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="414" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="415" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="416" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="417" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="418" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="419" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="420" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="421" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="422" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="423" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="432" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="433" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="434" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="435" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="436" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="437" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="438" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="439" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="440" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="441" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="442" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="443" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="444" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="445" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="446" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="447" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="448" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="449" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="450" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="451" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="452" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="453" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="454" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="455" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="456" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="457" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="458" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="459" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="460" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="461" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="462" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="463" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="464" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="465" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="466" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="467" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="468" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="469" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="470" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="471" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="472" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="473" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="474" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="475" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="476" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="477" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="478" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="479" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="480" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="481" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="482" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="483" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="484" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="485" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="486" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="487" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="488" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="489" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="490" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="491" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="492" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="493" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="494" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="495" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="496" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="497" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="498" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="499" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="500" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>12</v>
-      </c>
-      <c r="B501" t="s">
-        <v>13</v>
-      </c>
-      <c r="C501" t="s">
-        <v>14</v>
-      </c>
-      <c r="D501" t="s">
-        <v>15</v>
-      </c>
-      <c r="E501" t="s">
-        <v>16</v>
-      </c>
-      <c r="F501" t="s">
-        <v>17</v>
-      </c>
-      <c r="G501" t="s">
-        <v>18</v>
-      </c>
-      <c r="H501" t="s">
-        <v>19</v>
-      </c>
-      <c r="I501">
-        <v>8</v>
-      </c>
-      <c r="J501">
-        <v>25</v>
-      </c>
-      <c r="K501" t="s">
-        <v>20</v>
-      </c>
-      <c r="L501" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>21</v>
-      </c>
-      <c r="B502" t="s">
-        <v>22</v>
-      </c>
-      <c r="C502" t="s">
-        <v>23</v>
-      </c>
-      <c r="D502" t="s">
-        <v>15</v>
-      </c>
-      <c r="E502" t="s">
-        <v>16</v>
-      </c>
-      <c r="F502" t="s">
-        <v>24</v>
-      </c>
-      <c r="G502" t="s">
-        <v>19</v>
-      </c>
-      <c r="H502" t="s">
-        <v>19</v>
-      </c>
-      <c r="I502">
-        <v>45</v>
-      </c>
-      <c r="J502">
-        <v>120</v>
-      </c>
-      <c r="K502" t="s">
-        <v>25</v>
-      </c>
-      <c r="L502" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>26</v>
-      </c>
-      <c r="B503" t="s">
-        <v>27</v>
-      </c>
-      <c r="C503" t="s">
-        <v>23</v>
-      </c>
-      <c r="D503" t="s">
-        <v>28</v>
-      </c>
-      <c r="E503" t="s">
-        <v>16</v>
-      </c>
-      <c r="F503" t="s">
-        <v>17</v>
-      </c>
-      <c r="G503" t="s">
-        <v>19</v>
-      </c>
-      <c r="H503" t="s">
-        <v>19</v>
-      </c>
-      <c r="I503">
-        <v>12</v>
-      </c>
-      <c r="J503">
-        <v>40</v>
-      </c>
-      <c r="K503" t="s">
-        <v>29</v>
-      </c>
-      <c r="L503" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>30</v>
-      </c>
-      <c r="B504" t="s">
-        <v>31</v>
-      </c>
-      <c r="C504" t="s">
-        <v>32</v>
-      </c>
-      <c r="D504" t="s">
-        <v>33</v>
-      </c>
-      <c r="E504" t="s">
-        <v>16</v>
-      </c>
-      <c r="F504" t="s">
-        <v>24</v>
-      </c>
-      <c r="G504" t="s">
-        <v>19</v>
-      </c>
-      <c r="H504" t="s">
-        <v>19</v>
-      </c>
-      <c r="I504">
-        <v>55</v>
-      </c>
-      <c r="J504">
-        <v>140</v>
-      </c>
-      <c r="K504" t="s">
-        <v>34</v>
-      </c>
-      <c r="L504" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>35</v>
-      </c>
-      <c r="B505" t="s">
-        <v>36</v>
-      </c>
-      <c r="C505" t="s">
-        <v>32</v>
-      </c>
-      <c r="D505" t="s">
-        <v>37</v>
-      </c>
-      <c r="E505" t="s">
-        <v>16</v>
-      </c>
-      <c r="F505" t="s">
-        <v>17</v>
-      </c>
-      <c r="G505" t="s">
-        <v>19</v>
-      </c>
-      <c r="H505" t="s">
-        <v>19</v>
-      </c>
-      <c r="I505">
-        <v>40</v>
-      </c>
-      <c r="J505">
-        <v>110</v>
-      </c>
-      <c r="K505" t="s">
-        <v>38</v>
-      </c>
-      <c r="L505" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Diet" error="Choose one of: Veg, Jain, Non-veg" sqref="E10:E500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Diet" error="Choose one of: Veg, Jain, Non-veg" sqref="E10:E300">
       <formula1>"Veg,Jain,Non-veg"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Diet" error="Choose one of: Veg, Jain, Non-veg" sqref="E2:E500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Diet" error="Choose one of: Veg, Jain, Non-veg" sqref="E2:E300">
       <formula1>"Veg,Jain,Non-veg"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unit" error="Choose one of: plate, kg, piece, glass" sqref="G10:G500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unit" error="Choose one of: plate, kg, piece, glass" sqref="G10:G300">
       <formula1>"plate,kg,piece,glass"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unit" error="Choose one of: plate, kg, piece, glass" sqref="G2:G500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unit" error="Choose one of: plate, kg, piece, glass" sqref="G2:G300">
       <formula1>"plate,kg,piece,glass"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Priced" error="Choose one of: plate, counter, flat" sqref="H10:H500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Priced" error="Choose one of: plate, counter, flat" sqref="H10:H300">
       <formula1>"plate,counter,flat"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Priced" error="Choose one of: plate, counter, flat" sqref="H2:H500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Priced" error="Choose one of: plate, counter, flat" sqref="H2:H300">
       <formula1>"plate,counter,flat"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/import-examples/01 Menu items.xlsx
+++ b/docs/import-examples/01 Menu items.xlsx
@@ -85,7 +85,7 @@
     <comment ref="J1" authorId="0">
       <text>
         <r>
-          <t>Required. Selling price per plate (or per counter), in rupees. Numbers only.</t>
+          <t>Optional. Selling price per plate (or per counter), in rupees. Numbers only. Can be left blank and set later.</t>
         </r>
       </text>
     </comment>
@@ -663,7 +663,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">

--- a/docs/import-examples/01 Menu items.xlsx
+++ b/docs/import-examples/01 Menu items.xlsx
@@ -85,18 +85,26 @@
     <comment ref="J1" authorId="0">
       <text>
         <r>
-          <t>Optional. Selling price per plate (or per counter), in rupees. Numbers only. Can be left blank and set later.</t>
+          <t>Optional. Selling price per plate (or per counter), in rupees. Numbers only. Leave blank for main course dishes.</t>
         </r>
       </text>
     </comment>
     <comment ref="K1" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">Optional. Yes for main course dishes (Sabji, Dal, Kadhi, Rice, Khichdi, Breads, Sweets, Papad, Pickles, Salad). They need no price: the main course rate per plate is typed in at the end of each booking. Blank means No.
+Choose: Yes, No</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
           <t>Optional. One line for the menu card.</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <t>Optional. Optional web link to a photo. You can also add photos in bulk on the Import page.</t>
@@ -108,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -140,6 +148,9 @@
     <t>Price</t>
   </si>
   <si>
+    <t>Main course</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -170,6 +181,9 @@
     <t>plate</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Spiced buttermilk with roasted cumin and mint</t>
   </si>
   <si>
@@ -188,43 +202,52 @@
     <t>Chargrilled cottage cheese with mint chutney</t>
   </si>
   <si>
-    <t>Khaman Dhokla</t>
-  </si>
-  <si>
-    <t>ખમણ ઢોકળા</t>
-  </si>
-  <si>
-    <t>Farsan</t>
-  </si>
-  <si>
-    <t>Soft steamed gram flour cake</t>
-  </si>
-  <si>
     <t>Paneer Butter Masala</t>
   </si>
   <si>
     <t>પનીર બટર મસાલા</t>
   </si>
   <si>
-    <t>Main course</t>
-  </si>
-  <si>
-    <t>Sabji &gt; Paneer sabji</t>
+    <t>Sabji</t>
+  </si>
+  <si>
+    <t>Paneer sabji</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
   <si>
     <t>Paneer in a rich tomato and butter gravy</t>
   </si>
   <si>
-    <t>Undhiyu</t>
-  </si>
-  <si>
-    <t>ઊંધિયું</t>
-  </si>
-  <si>
-    <t>Sabji &gt; Gujarati sabji</t>
-  </si>
-  <si>
-    <t>Winter mixed vegetables, slow cooked</t>
+    <t>Gujarati Dal</t>
+  </si>
+  <si>
+    <t>ગુજરાતી દાળ</t>
+  </si>
+  <si>
+    <t>Dal</t>
+  </si>
+  <si>
+    <t>Jain</t>
+  </si>
+  <si>
+    <t>Sweet and sour toor dal</t>
+  </si>
+  <si>
+    <t>Gulab Jamun</t>
+  </si>
+  <si>
+    <t>ગુલાબ જાંબુ</t>
+  </si>
+  <si>
+    <t>Sweets</t>
+  </si>
+  <si>
+    <t>piece</t>
+  </si>
+  <si>
+    <t>Served warm</t>
   </si>
 </sst>
 </file>
@@ -621,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L300"/>
+  <dimension ref="A1:M300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -631,11 +654,12 @@
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="40" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,31 +696,34 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -705,36 +732,39 @@
         <v>25</v>
       </c>
       <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>45</v>
@@ -743,422 +773,434 @@
         <v>120</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5">
         <v>15</v>
       </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6">
         <v>15</v>
       </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5">
-        <v>55</v>
-      </c>
-      <c r="J5">
-        <v>140</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>40</v>
-      </c>
-      <c r="J6">
-        <v>110</v>
-      </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="266" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="267" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="270" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="273" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="274" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="275" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="276" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="289" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="291" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="292" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="293" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="294" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="295" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="296" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="5:8" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="5:8" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="5:11" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="5:11" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Diet" error="Choose one of: Veg, Jain, Non-veg" sqref="E10:E300">
       <formula1>"Veg,Jain,Non-veg"</formula1>
     </dataValidation>
@@ -1177,6 +1219,12 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Priced" error="Choose one of: plate, counter, flat" sqref="H2:H300">
       <formula1>"plate,counter,flat"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Main course" error="Choose one of: Yes, No" sqref="K10:K300">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Main course" error="Choose one of: Yes, No" sqref="K2:K300">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
